--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488230_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488230_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.5319</v>
+        <v>7.6122</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8454</v>
+        <v>6.0735</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6864</v>
+        <v>1.5387</v>
       </c>
       <c r="G2" t="n">
         <v>4.5962</v>
@@ -610,13 +610,13 @@
         <v>2.4087</v>
       </c>
       <c r="S2" t="n">
-        <v>1.788</v>
+        <v>0.8683</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6477</v>
+        <v>0.8758</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1402</v>
+        <v>-0.0075</v>
       </c>
       <c r="V2" t="n">
         <v>2.5183</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>J. RIBEIROS CARREIRAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.584</v>
+        <v>6.5156</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1604</v>
+        <v>4.0088</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4235</v>
+        <v>2.5069</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9313</v>
+        <v>8.1319</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0202</v>
+        <v>1.2785</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9111</v>
+        <v>6.8534</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9272</v>
+        <v>8.081</v>
       </c>
       <c r="K3" t="n">
-        <v>1.554</v>
+        <v>1.5889</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3732</v>
+        <v>6.4921</v>
       </c>
       <c r="M3" t="n">
-        <v>0.004</v>
+        <v>0.0509</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5338000000000001</v>
+        <v>-0.3104</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5379</v>
+        <v>0.3613</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9264</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9264</v>
+        <v>-4.6322</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8529</v>
+        <v>2.9646</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9862</v>
+        <v>0.0513</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7907</v>
+        <v>0.5599</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1955</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.26</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6311</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5477</v>
+        <v>3.7463</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9351</v>
+        <v>3.0105</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6127</v>
+        <v>0.7358</v>
       </c>
       <c r="G4" t="n">
         <v>2.9518</v>
@@ -766,13 +766,13 @@
         <v>1.4823</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7436</v>
+        <v>-0.0578</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3779</v>
+        <v>0.4533</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6342</v>
+        <v>-0.5111</v>
       </c>
       <c r="V4" t="n">
         <v>-0.63</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. RIBEIROS CARREIRAS</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.4394</v>
+        <v>3.348</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3757</v>
+        <v>1.737</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0637</v>
+        <v>1.611</v>
       </c>
       <c r="G5" t="n">
-        <v>8.1319</v>
+        <v>1.9313</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2785</v>
+        <v>1.0202</v>
       </c>
       <c r="I5" t="n">
-        <v>6.8534</v>
+        <v>0.9111</v>
       </c>
       <c r="J5" t="n">
-        <v>8.081</v>
+        <v>1.9272</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5889</v>
+        <v>1.554</v>
       </c>
       <c r="L5" t="n">
-        <v>6.4921</v>
+        <v>0.3732</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0509</v>
+        <v>0.004</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3104</v>
+        <v>-0.5338000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3613</v>
+        <v>0.5379</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.6322</v>
+        <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9646</v>
+        <v>1.8529</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.025</v>
+        <v>1.7503</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0732</v>
+        <v>1.3673</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9518</v>
+        <v>0.383</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.26</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6311</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0529</v>
+        <v>0.3689</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2472</v>
+        <v>0.6936</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3001</v>
+        <v>-0.3247</v>
       </c>
       <c r="G6" t="n">
         <v>1.3952</v>
@@ -922,13 +922,13 @@
         <v>0.7411</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9304</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5471</v>
+        <v>-0.1007</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3833</v>
+        <v>-0.4079</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2589</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5153</v>
+        <v>-0.8949</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4328</v>
+        <v>1.9546</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.948</v>
+        <v>-2.8495</v>
       </c>
       <c r="G7" t="n">
         <v>-1.0012</v>
@@ -1000,13 +1000,13 @@
         <v>2.0382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3355</v>
+        <v>-0.0441</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1043</v>
+        <v>0.6261</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7688</v>
+        <v>-0.6703</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8877</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6531</v>
+        <v>-1.7345</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.2339</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7222</v>
+        <v>-1.5006</v>
       </c>
       <c r="G8" t="n">
         <v>-5.5723</v>
@@ -1078,13 +1078,13 @@
         <v>2.2234</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9304</v>
+        <v>-0.0118</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3656</v>
+        <v>0.3314</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5648</v>
+        <v>-0.3432</v>
       </c>
       <c r="V8" t="n">
         <v>4.4054</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.7885</v>
+        <v>-6.0477</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.2459</v>
+        <v>-4.6036</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5426</v>
+        <v>-1.4441</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6422</v>
@@ -1156,13 +1156,13 @@
         <v>1.1117</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9789</v>
+        <v>-0.2381</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6019</v>
+        <v>0.0404</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3771</v>
+        <v>-0.2786</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5733</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>12.0932</v>
+        <v>12.9139</v>
       </c>
       <c r="E10" t="n">
-        <v>11.8198</v>
+        <v>12.6405</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2733999999999996</v>
+        <v>0.2735000000000003</v>
       </c>
       <c r="G10" t="n">
         <v>10.7907</v>
@@ -1213,19 +1213,19 @@
         <v>4.772700000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>9.099099999999998</v>
+        <v>9.0991</v>
       </c>
       <c r="M10" t="n">
         <v>-3.0812</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.119800000000001</v>
+        <v>-4.1198</v>
       </c>
       <c r="O10" t="n">
         <v>1.0388</v>
       </c>
       <c r="P10" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="Q10" t="n">
         <v>-14.8229</v>
@@ -1234,16 +1234,16 @@
         <v>14.8229</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9886000000000008</v>
+        <v>1.8095</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3328</v>
+        <v>4.1535</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.3443</v>
+        <v>-2.3442</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3138000000000006</v>
+        <v>0.3138000000000005</v>
       </c>
       <c r="W10" t="n">
         <v>9.4381</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. HEPBURN</t>
+          <t>J. REYES BARRANCO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2.984</v>
+        <v>2.1313</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0743</v>
+        <v>2.4551</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.3238</v>
       </c>
       <c r="G11" t="n">
-        <v>1.6036</v>
+        <v>-2.6359</v>
       </c>
       <c r="H11" t="n">
-        <v>2.052</v>
+        <v>2.5545</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4484</v>
+        <v>-5.1905</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5747</v>
+        <v>-0.1223</v>
       </c>
       <c r="K11" t="n">
-        <v>3.0617</v>
+        <v>3.5555</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.487</v>
+        <v>-3.6778</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9711</v>
+        <v>-2.5137</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0097</v>
+        <v>-1.001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0386</v>
+        <v>-1.5127</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2234</v>
+        <v>2.7793</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6387</v>
+        <v>-0.2503</v>
       </c>
       <c r="T11" t="n">
-        <v>1.7236</v>
+        <v>0.3392</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0848</v>
+        <v>-0.5895</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6289</v>
+        <v>4.091</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6289</v>
+        <v>4.091</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2578</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. GALLEGO GÓMEZ</t>
+          <t>P. HEPBURN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.8883</v>
+        <v>1.9624</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8883</v>
+        <v>2.1929</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-0.2305</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8883</v>
+        <v>1.6036</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6441</v>
+        <v>2.052</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2441</v>
+        <v>-0.4484</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8883</v>
+        <v>2.5747</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6441</v>
+        <v>3.0617</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2441</v>
+        <v>-0.487</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>-0.9711</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>-1.0097</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.0386</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.2234</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.6171</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0.2251</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2578</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. REYES BARRANCO</t>
+          <t>A. GALLEGO GÓMEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9791</v>
+        <v>1.8883</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5737</v>
+        <v>1.8883</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5947</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.6359</v>
+        <v>1.8883</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5545</v>
+        <v>0.6441</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.1905</v>
+        <v>1.2441</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1223</v>
+        <v>1.8883</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5555</v>
+        <v>0.6441</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.6778</v>
+        <v>1.2441</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.5137</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.001</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.5127</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7793</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4025</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5422</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8603</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>4.091</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>4.091</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9359</v>
+        <v>1.433</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4676</v>
+        <v>0.9573</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4683</v>
+        <v>0.4757</v>
       </c>
       <c r="G14" t="n">
         <v>1.2802</v>
@@ -1546,13 +1546,13 @@
         <v>2.2234</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7138</v>
+        <v>-0.2167</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2139</v>
+        <v>0.2758</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4999</v>
+        <v>-0.4925</v>
       </c>
       <c r="V14" t="n">
         <v>-0.0011</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4596</v>
+        <v>-0.4104</v>
       </c>
       <c r="E15" t="n">
         <v>-0.1094</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3502</v>
+        <v>-0.3009</v>
       </c>
       <c r="G15" t="n">
         <v>-0.3071</v>
@@ -1624,13 +1624,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1525</v>
+        <v>-0.1032</v>
       </c>
       <c r="T15" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.043</v>
+        <v>0.0062</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7817</v>
+        <v>-0.9444</v>
       </c>
       <c r="E16" t="n">
-        <v>2.444</v>
+        <v>2.0523</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.2257</v>
+        <v>-2.9967</v>
       </c>
       <c r="G16" t="n">
         <v>-3.6728</v>
@@ -1702,13 +1702,13 @@
         <v>2.2234</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0197</v>
+        <v>-0.143</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9066</v>
+        <v>0.5149</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8869</v>
+        <v>-0.6579</v>
       </c>
       <c r="V16" t="n">
         <v>1.5744</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.7294</v>
+        <v>-2.7219</v>
       </c>
       <c r="E17" t="n">
         <v>-1.4456</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2838</v>
+        <v>-1.2763</v>
       </c>
       <c r="G17" t="n">
         <v>0.8193</v>
@@ -1780,13 +1780,13 @@
         <v>1.297</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5285</v>
+        <v>-0.521</v>
       </c>
       <c r="T17" t="n">
         <v>-0.1256</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4029</v>
+        <v>-0.3955</v>
       </c>
       <c r="V17" t="n">
         <v>0.315</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.6974</v>
+        <v>-3.4683</v>
       </c>
       <c r="E18" t="n">
         <v>-1.6698</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.0276</v>
+        <v>-1.7985</v>
       </c>
       <c r="G18" t="n">
         <v>-2.2716</v>
@@ -1858,13 +1858,13 @@
         <v>1.6676</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0532</v>
+        <v>0.2823</v>
       </c>
       <c r="T18" t="n">
         <v>0.1816</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1283</v>
+        <v>0.1007</v>
       </c>
       <c r="V18" t="n">
         <v>-3.1466</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>A. GALLEGO GOMEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.5869</v>
+        <v>-5.649</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7382</v>
+        <v>-3.9541</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8487</v>
+        <v>-1.6948</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.7603</v>
+        <v>-4.7344</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2322</v>
+        <v>-1.5349</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.5281</v>
+        <v>-3.1994</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8269</v>
+        <v>-2.4874</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4643</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3626</v>
+        <v>-1.7098</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9334</v>
+        <v>-2.247</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2322</v>
+        <v>-0.7573</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1656</v>
+        <v>-1.4897</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R19" t="n">
-        <v>1.297</v>
+        <v>1.1117</v>
       </c>
       <c r="S19" t="n">
-        <v>0.247</v>
+        <v>-0.1735</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0584</v>
+        <v>0.3861</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3054</v>
+        <v>-0.5596</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.5177</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.5177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. GALLEGO GOMEZ</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.6255</v>
+        <v>-5.6613</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.7583</v>
+        <v>-2.6402</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8672</v>
+        <v>-3.0211</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.7344</v>
+        <v>-2.7603</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5349</v>
+        <v>-0.2322</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.1994</v>
+        <v>-2.5281</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.4874</v>
+        <v>-0.8269</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.4643</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.7098</v>
+        <v>-0.3626</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.247</v>
+        <v>-1.9334</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7573</v>
+        <v>0.2322</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4897</v>
+        <v>-2.1656</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7411</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1117</v>
+        <v>1.297</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.15</v>
+        <v>0.1725</v>
       </c>
       <c r="T20" t="n">
-        <v>0.582</v>
+        <v>0.0395</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.732</v>
+        <v>0.133</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.5177</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="21">
@@ -2047,19 +2047,19 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-12.0932</v>
+        <v>-11.4403</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2734000000000005</v>
+        <v>-0.2732000000000006</v>
       </c>
       <c r="F21" t="n">
-        <v>-11.8199</v>
+        <v>-11.1669</v>
       </c>
       <c r="G21" t="n">
         <v>-10.7907</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6528000000000007</v>
+        <v>-0.6527999999999998</v>
       </c>
       <c r="I21" t="n">
         <v>-10.1379</v>
@@ -2092,13 +2092,13 @@
         <v>14.8228</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9886999999999997</v>
+        <v>-0.3358</v>
       </c>
       <c r="T21" t="n">
         <v>2.3443</v>
       </c>
       <c r="U21" t="n">
-        <v>-3.3327</v>
+        <v>-2.6802</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3138999999999998</v>
